--- a/results/MVSE/freebase/MVSE_freebase<l03>AllRes_61.41.xlsx
+++ b/results/MVSE/freebase/MVSE_freebase<l03>AllRes_61.41.xlsx
@@ -481,48 +481,48 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>nce_k</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>avg_loss</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>avg_test_mif1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>std_loss</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>std_test_mif1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>config2str</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>walk_hop</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>avg_loss</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>avg_test_mif1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>std_loss</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>std_test_mif1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>config2str</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>nce_k</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>4096</v>
       </c>
       <c r="M2" t="n">
         <v>2</v>
@@ -592,12 +592,12 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>4096</v>
       </c>
       <c r="M3" t="n">
         <v>2</v>
@@ -667,12 +667,12 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>4096</v>
       </c>
       <c r="M4" t="n">
         <v>2</v>
@@ -742,12 +742,12 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="M5" t="n">
         <v>2</v>
@@ -817,12 +817,12 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="M6" t="n">
         <v>2</v>
@@ -892,12 +892,12 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="M7" t="n">
         <v>2</v>
@@ -967,12 +967,12 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>4096</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
@@ -1042,12 +1042,12 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>4096</v>
       </c>
       <c r="M9" t="n">
         <v>2</v>
@@ -1117,12 +1117,12 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>4096</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
@@ -1192,12 +1192,12 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>4096</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>8192</v>
       </c>
       <c r="M11" t="n">
         <v>2</v>
@@ -1267,12 +1267,12 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>8192</v>
       </c>
       <c r="M12" t="n">
         <v>2</v>
@@ -1342,12 +1342,12 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>4096</v>
       </c>
       <c r="M13" t="n">
         <v>2</v>
@@ -1417,12 +1417,12 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>4096</v>
       </c>
       <c r="M14" t="n">
         <v>2</v>
@@ -1492,12 +1492,12 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>4096</v>
       </c>
       <c r="M15" t="n">
         <v>2</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>8192</v>
       </c>
       <c r="M16" t="n">
         <v>2</v>
@@ -1642,12 +1642,12 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>4096</v>
       </c>
       <c r="M17" t="n">
         <v>2</v>
@@ -1717,12 +1717,12 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>8192</v>
       </c>
       <c r="M18" t="n">
         <v>2</v>
@@ -1792,12 +1792,12 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="M19" t="n">
         <v>2</v>
@@ -1867,12 +1867,12 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>4096</v>
       </c>
       <c r="M20" t="n">
         <v>2</v>
@@ -1942,12 +1942,12 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>8192</v>
       </c>
       <c r="M21" t="n">
         <v>2</v>
@@ -2017,12 +2017,12 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="M22" t="n">
         <v>2</v>
@@ -2092,12 +2092,12 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>8192</v>
       </c>
       <c r="M23" t="n">
         <v>2</v>
@@ -2167,12 +2167,12 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>8192</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>4096</v>
       </c>
       <c r="M24" t="n">
         <v>2</v>
@@ -2242,12 +2242,12 @@
         </is>
       </c>
       <c r="S24" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>4096</v>
       </c>
       <c r="M25" t="n">
         <v>2</v>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="S25" t="n">
-        <v>4096</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
